--- a/resources/templates/standard/K2100-06.xlsx
+++ b/resources/templates/standard/K2100-06.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>선입선출 관리 기준서</t>
   </si>
@@ -534,12 +537,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -574,21 +579,21 @@
       <c r="AJ1" s="2"/>
       <c r="AK1" s="2"/>
       <c r="AL1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM1" s="3"/>
       <c r="AN1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO1" s="4"/>
       <c r="AP1" s="4"/>
       <c r="AQ1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR1" s="4"/>
       <c r="AS1" s="4"/>
       <c r="AT1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU1" s="4"/>
       <c r="AV1" s="4"/>
@@ -1245,11 +1250,11 @@
     </row>
     <row r="15" ht="20.1" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
@@ -1257,7 +1262,7 @@
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
       <c r="I15" s="8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J15" s="8"/>
       <c r="K15" s="8"/>
@@ -1265,7 +1270,7 @@
       <c r="M15" s="8"/>
       <c r="N15" s="8"/>
       <c r="O15" s="8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P15" s="8"/>
       <c r="Q15" s="8"/>
@@ -1295,7 +1300,7 @@
       <c r="AO15" s="8"/>
       <c r="AP15" s="8"/>
       <c r="AQ15" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR15" s="8"/>
       <c r="AS15" s="8"/>
@@ -1605,7 +1610,7 @@
     </row>
     <row r="22" ht="20.1" customHeight="1" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="10"/>
